--- a/artfynd/A 11492-2022 artfynd.xlsx
+++ b/artfynd/A 11492-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11492-2022 artfynd.xlsx
+++ b/artfynd/A 11492-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7453,6 +7453,934 @@
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>120536905</v>
+      </c>
+      <c r="B61" t="n">
+        <v>90864</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>658</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lidgatu, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>599672</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7034647</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>120536902</v>
+      </c>
+      <c r="B62" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lidgatu, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>599814</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7034812</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120536900</v>
+      </c>
+      <c r="B63" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lidgatu, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>599871</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7034818</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>120536903</v>
+      </c>
+      <c r="B64" t="n">
+        <v>90864</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>658</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lidgatu, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>599813</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7034818</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120536901</v>
+      </c>
+      <c r="B65" t="n">
+        <v>90864</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>658</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lidgatu, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>599866</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7034826</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>120536906</v>
+      </c>
+      <c r="B66" t="n">
+        <v>86895</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>510</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lidgatu, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>599641</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7034506</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>120536907</v>
+      </c>
+      <c r="B67" t="n">
+        <v>91023</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lidgatu, Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>599620</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7034514</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>120536904</v>
+      </c>
+      <c r="B68" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lidgatu, Ång</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>599766</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7034808</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11492-2022 artfynd.xlsx
+++ b/artfynd/A 11492-2022 artfynd.xlsx
@@ -7455,7 +7455,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120536905</v>
+        <v>120536901</v>
       </c>
       <c r="B61" t="n">
         <v>90864</v>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>599672</v>
+        <v>599866</v>
       </c>
       <c r="R61" t="n">
-        <v>7034647</v>
+        <v>7034826</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7529,22 +7529,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7571,7 +7571,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120536902</v>
+        <v>120536904</v>
       </c>
       <c r="B62" t="n">
         <v>90580</v>
@@ -7615,10 +7615,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>599814</v>
+        <v>599766</v>
       </c>
       <c r="R62" t="n">
-        <v>7034812</v>
+        <v>7034808</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7687,10 +7687,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120536900</v>
+        <v>120536905</v>
       </c>
       <c r="B63" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7703,21 +7703,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7731,10 +7731,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>599871</v>
+        <v>599672</v>
       </c>
       <c r="R63" t="n">
-        <v>7034818</v>
+        <v>7034647</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7761,22 +7761,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7803,10 +7803,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120536903</v>
+        <v>120536902</v>
       </c>
       <c r="B64" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7819,21 +7819,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7847,10 +7847,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>599813</v>
+        <v>599814</v>
       </c>
       <c r="R64" t="n">
-        <v>7034818</v>
+        <v>7034812</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7919,10 +7919,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120536901</v>
+        <v>120536900</v>
       </c>
       <c r="B65" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7935,21 +7935,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7963,10 +7963,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>599866</v>
+        <v>599871</v>
       </c>
       <c r="R65" t="n">
-        <v>7034826</v>
+        <v>7034818</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7998,7 +7998,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8267,10 +8267,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120536904</v>
+        <v>120536903</v>
       </c>
       <c r="B68" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8283,21 +8283,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>599766</v>
+        <v>599813</v>
       </c>
       <c r="R68" t="n">
-        <v>7034808</v>
+        <v>7034818</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 11492-2022 artfynd.xlsx
+++ b/artfynd/A 11492-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2517,10 +2517,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>105157766</v>
+        <v>105157764</v>
       </c>
       <c r="B18" t="n">
-        <v>78569</v>
+        <v>94121</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2533,21 +2533,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599780.4218307084</v>
+        <v>599601.5465131965</v>
       </c>
       <c r="R18" t="n">
-        <v>7034674.422484341</v>
+        <v>7034670.186768517</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2633,10 +2633,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>105157764</v>
+        <v>105157769</v>
       </c>
       <c r="B19" t="n">
-        <v>94121</v>
+        <v>77506</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2649,21 +2649,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599601.5465131965</v>
+        <v>599760.5181248389</v>
       </c>
       <c r="R19" t="n">
-        <v>7034670.186768517</v>
+        <v>7034665.288410758</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2749,7 +2749,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>105157769</v>
+        <v>109632757</v>
       </c>
       <c r="B20" t="n">
         <v>77506</v>
@@ -2783,19 +2783,22 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Blåbärshällorna, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599760.5181248389</v>
+        <v>599714.0405093244</v>
       </c>
       <c r="R20" t="n">
-        <v>7034665.288410758</v>
+        <v>7034616.34561114</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2819,7 +2822,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-08-07</t>
+          <t>2023-05-29</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -2829,7 +2832,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-08-07</t>
+          <t>2023-05-29</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -2843,32 +2846,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>109632757</v>
+        <v>109632850</v>
       </c>
       <c r="B21" t="n">
-        <v>77506</v>
+        <v>96334</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2877,30 +2877,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2908,13 +2909,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599714.0405093244</v>
+        <v>599658.2109749377</v>
       </c>
       <c r="R21" t="n">
-        <v>7034616.34561114</v>
+        <v>7034622.668968407</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2981,10 +2982,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>109632850</v>
+        <v>109632333</v>
       </c>
       <c r="B22" t="n">
-        <v>96334</v>
+        <v>77541</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2993,31 +2994,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3025,13 +3025,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599658.2109749377</v>
+        <v>599741.1976426356</v>
       </c>
       <c r="R22" t="n">
-        <v>7034622.668968407</v>
+        <v>7034766.836296913</v>
       </c>
       <c r="S22" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3098,10 +3098,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>109632333</v>
+        <v>109632765</v>
       </c>
       <c r="B23" t="n">
-        <v>77541</v>
+        <v>89392</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3114,21 +3114,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599741.1976426356</v>
+        <v>599670.5126179606</v>
       </c>
       <c r="R23" t="n">
-        <v>7034766.836296913</v>
+        <v>7034659.791880115</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3214,10 +3214,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>109632765</v>
+        <v>109747883</v>
       </c>
       <c r="B24" t="n">
-        <v>89392</v>
+        <v>96334</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3226,44 +3226,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Blåbärshällorna, Ång</t>
+          <t>Blåbärhällorna, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599670.5126179606</v>
+        <v>599722.3444800271</v>
       </c>
       <c r="R24" t="n">
-        <v>7034659.791880115</v>
+        <v>7034594.650477036</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3287,22 +3289,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-05-29</t>
+          <t>2023-06-03</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-05-29</t>
+          <t>2023-06-03</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3311,26 +3313,25 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>109747883</v>
+        <v>109747196</v>
       </c>
       <c r="B25" t="n">
         <v>96334</v>
@@ -3363,22 +3364,18 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Blåbärhällorna, Ång</t>
+          <t>Hömyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599722.3444800271</v>
+        <v>599795.6598234512</v>
       </c>
       <c r="R25" t="n">
-        <v>7034594.650477036</v>
+        <v>7034660.561076441</v>
       </c>
       <c r="S25" t="n">
         <v>2</v>
@@ -3410,7 +3407,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3420,7 +3417,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3435,22 +3432,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>109747196</v>
+        <v>109748320</v>
       </c>
       <c r="B26" t="n">
-        <v>96334</v>
+        <v>89392</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3459,42 +3456,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hömyrtjärnen, Ång</t>
+          <t>Blåbärhällorna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599795.6598234512</v>
+        <v>599675.9290269429</v>
       </c>
       <c r="R26" t="n">
-        <v>7034660.561076441</v>
+        <v>7034486.117542973</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3523,7 +3520,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3533,7 +3530,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3548,22 +3545,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>109748320</v>
+        <v>109747673</v>
       </c>
       <c r="B27" t="n">
-        <v>89392</v>
+        <v>96334</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3572,28 +3569,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3601,13 +3602,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599675.9290269429</v>
+        <v>599717.9893236528</v>
       </c>
       <c r="R27" t="n">
-        <v>7034486.117542973</v>
+        <v>7034604.819653061</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3636,7 +3637,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3646,7 +3647,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3661,19 +3662,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>109747673</v>
+        <v>109748114</v>
       </c>
       <c r="B28" t="n">
         <v>96334</v>
@@ -3708,7 +3709,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3718,10 +3719,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599717.9893236528</v>
+        <v>599710.2792120088</v>
       </c>
       <c r="R28" t="n">
-        <v>7034604.819653061</v>
+        <v>7034535.579332849</v>
       </c>
       <c r="S28" t="n">
         <v>2</v>
@@ -3753,7 +3754,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3763,7 +3764,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3778,22 +3779,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>109748114</v>
+        <v>109748169</v>
       </c>
       <c r="B29" t="n">
-        <v>96334</v>
+        <v>56395</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3802,46 +3803,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Blåbärhällorna, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>599710.2792120088</v>
+        <v>599692.1114921889</v>
       </c>
       <c r="R29" t="n">
-        <v>7034535.579332849</v>
+        <v>7034528.291748884</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3870,7 +3872,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3880,7 +3882,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3895,22 +3897,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>109748169</v>
+        <v>109747391</v>
       </c>
       <c r="B30" t="n">
-        <v>56395</v>
+        <v>78569</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3923,43 +3925,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Blåbärhällorna, Ång</t>
+          <t>Hömyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>599692.1114921889</v>
+        <v>599771.2610742658</v>
       </c>
       <c r="R30" t="n">
-        <v>7034528.291748884</v>
+        <v>7034666.071814045</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3988,7 +3985,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3998,7 +3995,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4013,22 +4010,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>109747391</v>
+        <v>109751333</v>
       </c>
       <c r="B31" t="n">
-        <v>78569</v>
+        <v>96334</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4037,39 +4034,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hömyrtjärnen, Ång</t>
+          <t>Blåbärhällorna, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>599771.2610742658</v>
+        <v>599620.4478943436</v>
       </c>
       <c r="R31" t="n">
-        <v>7034666.071814045</v>
+        <v>7034495.589255284</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
@@ -4101,7 +4102,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4111,7 +4112,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4126,19 +4127,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>109751333</v>
+        <v>109751423</v>
       </c>
       <c r="B32" t="n">
         <v>96334</v>
@@ -4183,10 +4184,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>599620.4478943436</v>
+        <v>599623.0866702336</v>
       </c>
       <c r="R32" t="n">
-        <v>7034495.589255284</v>
+        <v>7034540.477186345</v>
       </c>
       <c r="S32" t="n">
         <v>2</v>
@@ -4218,7 +4219,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4228,7 +4229,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4255,10 +4256,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>109751423</v>
+        <v>109747426</v>
       </c>
       <c r="B33" t="n">
-        <v>96334</v>
+        <v>89410</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4267,43 +4268,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Blåbärhällorna, Ång</t>
+          <t>Hömyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>599623.0866702336</v>
+        <v>599757.9513025703</v>
       </c>
       <c r="R33" t="n">
-        <v>7034540.477186345</v>
+        <v>7034618.163994164</v>
       </c>
       <c r="S33" t="n">
         <v>2</v>
@@ -4335,7 +4332,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4345,7 +4342,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4372,10 +4369,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>109747426</v>
+        <v>109747674</v>
       </c>
       <c r="B34" t="n">
-        <v>89410</v>
+        <v>77258</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4388,21 +4385,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4413,10 +4410,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>599757.9513025703</v>
+        <v>599698.6504620004</v>
       </c>
       <c r="R34" t="n">
-        <v>7034618.163994164</v>
+        <v>7034649.468588625</v>
       </c>
       <c r="S34" t="n">
         <v>2</v>
@@ -4448,7 +4445,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4458,7 +4455,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4473,22 +4470,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>109747674</v>
+        <v>109746436</v>
       </c>
       <c r="B35" t="n">
-        <v>77258</v>
+        <v>89356</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4497,25 +4494,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4526,13 +4523,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>599698.6504620004</v>
+        <v>599769.5241476779</v>
       </c>
       <c r="R35" t="n">
-        <v>7034649.468588625</v>
+        <v>7034664.225438554</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4561,7 +4558,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4571,7 +4568,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4586,22 +4583,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>109746436</v>
+        <v>109749485</v>
       </c>
       <c r="B36" t="n">
-        <v>89356</v>
+        <v>96334</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4610,42 +4607,46 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hömyrtjärnen, Ång</t>
+          <t>Blåbärhällorna, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599769.5241476779</v>
+        <v>599586.9967295172</v>
       </c>
       <c r="R36" t="n">
-        <v>7034664.225438554</v>
+        <v>7034374.016439344</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4674,7 +4675,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4684,7 +4685,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4699,22 +4700,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>109749485</v>
+        <v>109746440</v>
       </c>
       <c r="B37" t="n">
-        <v>96334</v>
+        <v>78569</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4723,43 +4724,39 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Blåbärhällorna, Ång</t>
+          <t>Hömyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>599586.9967295172</v>
+        <v>599857.5581023413</v>
       </c>
       <c r="R37" t="n">
-        <v>7034374.016439344</v>
+        <v>7034747.172792366</v>
       </c>
       <c r="S37" t="n">
         <v>2</v>
@@ -4791,7 +4788,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4801,7 +4798,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På Björk</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4828,10 +4830,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>109746440</v>
+        <v>109747956</v>
       </c>
       <c r="B38" t="n">
-        <v>78569</v>
+        <v>96334</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4840,39 +4842,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hömyrtjärnen, Ång</t>
+          <t>Blåbärhällorna, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>599857.5581023413</v>
+        <v>599743.5071849127</v>
       </c>
       <c r="R38" t="n">
-        <v>7034747.172792366</v>
+        <v>7034577.836993911</v>
       </c>
       <c r="S38" t="n">
         <v>2</v>
@@ -4904,7 +4906,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4914,12 +4916,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På Björk</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4946,7 +4943,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>109747956</v>
+        <v>109747422</v>
       </c>
       <c r="B39" t="n">
         <v>96334</v>
@@ -4983,14 +4980,14 @@
       <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Blåbärhällorna, Ång</t>
+          <t>Hömyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>599743.5071849127</v>
+        <v>599773.4322296742</v>
       </c>
       <c r="R39" t="n">
-        <v>7034577.836993911</v>
+        <v>7034668.379783352</v>
       </c>
       <c r="S39" t="n">
         <v>2</v>
@@ -5022,7 +5019,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5032,7 +5029,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5047,22 +5044,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>109747422</v>
+        <v>109747467</v>
       </c>
       <c r="B40" t="n">
-        <v>96334</v>
+        <v>89673</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5071,25 +5068,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5100,13 +5097,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599773.4322296742</v>
+        <v>599715.0639328548</v>
       </c>
       <c r="R40" t="n">
-        <v>7034668.379783352</v>
+        <v>7034626.682537876</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5135,7 +5132,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5145,7 +5142,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5160,19 +5157,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>109747467</v>
+        <v>109747404</v>
       </c>
       <c r="B41" t="n">
         <v>89673</v>
@@ -5213,13 +5210,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599715.0639328548</v>
+        <v>599767.9248166137</v>
       </c>
       <c r="R41" t="n">
-        <v>7034626.682537876</v>
+        <v>7034629.22836843</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5248,7 +5245,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5258,7 +5255,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5273,19 +5270,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>109747404</v>
+        <v>109746428</v>
       </c>
       <c r="B42" t="n">
         <v>89673</v>
@@ -5326,13 +5323,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599767.9248166137</v>
+        <v>599769.5241476779</v>
       </c>
       <c r="R42" t="n">
-        <v>7034629.22836843</v>
+        <v>7034664.225438554</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5361,7 +5358,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5371,7 +5368,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5386,22 +5383,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>109746428</v>
+        <v>109747218</v>
       </c>
       <c r="B43" t="n">
-        <v>89673</v>
+        <v>89406</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5414,21 +5411,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5439,10 +5436,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599769.5241476779</v>
+        <v>599793.2650500382</v>
       </c>
       <c r="R43" t="n">
-        <v>7034664.225438554</v>
+        <v>7034665.414717777</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5474,7 +5471,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5484,7 +5481,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5511,10 +5508,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>109747218</v>
+        <v>109748041</v>
       </c>
       <c r="B44" t="n">
-        <v>89406</v>
+        <v>96334</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5523,42 +5520,46 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hömyrtjärnen, Ång</t>
+          <t>Blåbärhällorna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>599793.2650500382</v>
+        <v>599722.9424841346</v>
       </c>
       <c r="R44" t="n">
-        <v>7034665.414717777</v>
+        <v>7034546.727739297</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5587,7 +5588,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5597,7 +5598,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5612,19 +5613,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>109748041</v>
+        <v>109747184</v>
       </c>
       <c r="B45" t="n">
         <v>96334</v>
@@ -5659,20 +5660,20 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Blåbärhällorna, Ång</t>
+          <t>Hömyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599722.9424841346</v>
+        <v>599809.3165610553</v>
       </c>
       <c r="R45" t="n">
-        <v>7034546.727739297</v>
+        <v>7034668.604207011</v>
       </c>
       <c r="S45" t="n">
         <v>2</v>
@@ -5704,7 +5705,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5714,7 +5715,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5741,10 +5742,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>109747184</v>
+        <v>109747166</v>
       </c>
       <c r="B46" t="n">
-        <v>96334</v>
+        <v>96251</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5753,32 +5754,28 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5786,13 +5783,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599809.3165610553</v>
+        <v>599797.3967375822</v>
       </c>
       <c r="R46" t="n">
-        <v>7034668.604207011</v>
+        <v>7034662.407468742</v>
       </c>
       <c r="S46" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5846,22 +5843,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>109747166</v>
+        <v>109747042</v>
       </c>
       <c r="B47" t="n">
-        <v>96251</v>
+        <v>56395</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5870,42 +5867,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hömyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>599797.3967375822</v>
+        <v>599809.1636680734</v>
       </c>
       <c r="R47" t="n">
-        <v>7034662.407468742</v>
+        <v>7034687.86499245</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5934,7 +5936,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5944,7 +5946,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5959,22 +5961,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>109747042</v>
+        <v>109748316</v>
       </c>
       <c r="B48" t="n">
-        <v>56395</v>
+        <v>81236</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5987,40 +5989,35 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hömyrtjärnen, Ång</t>
+          <t>Blåbärhällorna, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>599809.1636680734</v>
+        <v>599652.4149206255</v>
       </c>
       <c r="R48" t="n">
-        <v>7034687.86499245</v>
+        <v>7034520.780971628</v>
       </c>
       <c r="S48" t="n">
         <v>2</v>
@@ -6052,7 +6049,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6062,7 +6059,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6077,22 +6074,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>109748316</v>
+        <v>109746431</v>
       </c>
       <c r="B49" t="n">
-        <v>81236</v>
+        <v>89392</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6105,38 +6102,38 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Blåbärhällorna, Ång</t>
+          <t>Hömyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>599652.4149206255</v>
+        <v>599769.5241476779</v>
       </c>
       <c r="R49" t="n">
-        <v>7034520.780971628</v>
+        <v>7034664.225438554</v>
       </c>
       <c r="S49" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6165,7 +6162,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6175,7 +6172,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6190,22 +6187,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>109746431</v>
+        <v>109746490</v>
       </c>
       <c r="B50" t="n">
-        <v>89392</v>
+        <v>77506</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6218,21 +6215,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6243,13 +6240,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599769.5241476779</v>
+        <v>599858.4824617859</v>
       </c>
       <c r="R50" t="n">
-        <v>7034664.225438554</v>
+        <v>7034746.305621488</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6278,7 +6275,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6288,7 +6285,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6303,22 +6300,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>109746490</v>
+        <v>109751380</v>
       </c>
       <c r="B51" t="n">
-        <v>77506</v>
+        <v>96334</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6327,39 +6324,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hömyrtjärnen, Ång</t>
+          <t>Blåbärhällorna, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>599858.4824617859</v>
+        <v>599625.1307146454</v>
       </c>
       <c r="R51" t="n">
-        <v>7034746.305621488</v>
+        <v>7034532.47592557</v>
       </c>
       <c r="S51" t="n">
         <v>2</v>
@@ -6391,7 +6392,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6401,7 +6402,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6428,10 +6429,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>109751380</v>
+        <v>109748313</v>
       </c>
       <c r="B52" t="n">
-        <v>96334</v>
+        <v>78503</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6440,32 +6441,28 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6473,13 +6470,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>599625.1307146454</v>
+        <v>599675.508716837</v>
       </c>
       <c r="R52" t="n">
-        <v>7034532.47592557</v>
+        <v>7034485.20831114</v>
       </c>
       <c r="S52" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6508,7 +6505,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6518,7 +6515,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6533,22 +6530,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>109748313</v>
+        <v>109747554</v>
       </c>
       <c r="B53" t="n">
-        <v>78503</v>
+        <v>89673</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6557,39 +6554,39 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Blåbärhällorna, Ång</t>
+          <t>Hömyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>599675.508716837</v>
+        <v>599743.986888607</v>
       </c>
       <c r="R53" t="n">
-        <v>7034485.20831114</v>
+        <v>7034619.968356109</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6621,7 +6618,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6631,7 +6628,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6658,10 +6655,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>109747554</v>
+        <v>109747618</v>
       </c>
       <c r="B54" t="n">
-        <v>89673</v>
+        <v>56411</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6674,25 +6671,30 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hömyrtjärnen, Ång</t>
@@ -6734,7 +6736,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6744,7 +6746,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6771,7 +6773,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>109747618</v>
+        <v>109746536</v>
       </c>
       <c r="B55" t="n">
         <v>56411</v>
@@ -6817,10 +6819,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>599743.986888607</v>
+        <v>599810.635818977</v>
       </c>
       <c r="R55" t="n">
-        <v>7034619.968356109</v>
+        <v>7034712.552797578</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6852,7 +6854,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6862,7 +6864,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6889,10 +6891,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>109746536</v>
+        <v>110589937</v>
       </c>
       <c r="B56" t="n">
-        <v>56411</v>
+        <v>96348</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6901,47 +6903,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hömyrtjärnen, Ång</t>
+          <t>Näsåker, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>599810.635818977</v>
+        <v>599613.4454346037</v>
       </c>
       <c r="R56" t="n">
-        <v>7034712.552797578</v>
+        <v>7034504.332183325</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6970,7 +6966,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6980,7 +6976,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6995,19 +6991,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Felicia Skorsdal</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Felicia Skorsdal</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>110589937</v>
+        <v>110589938</v>
       </c>
       <c r="B57" t="n">
         <v>96348</v>
@@ -7047,10 +7043,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>599613.4454346037</v>
+        <v>599783.6141665154</v>
       </c>
       <c r="R57" t="n">
-        <v>7034504.332183325</v>
+        <v>7034658.39280035</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -7119,10 +7115,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>110589938</v>
+        <v>110589933</v>
       </c>
       <c r="B58" t="n">
-        <v>96348</v>
+        <v>78604</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7131,25 +7127,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7159,10 +7155,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>599783.6141665154</v>
+        <v>599656.8768513317</v>
       </c>
       <c r="R58" t="n">
-        <v>7034658.39280035</v>
+        <v>7034464.016388355</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7231,10 +7227,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>110589933</v>
+        <v>110589936</v>
       </c>
       <c r="B59" t="n">
-        <v>78604</v>
+        <v>78578</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7243,25 +7239,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7271,10 +7267,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>599656.8768513317</v>
+        <v>599856.2841013347</v>
       </c>
       <c r="R59" t="n">
-        <v>7034464.016388355</v>
+        <v>7034759.22969401</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7343,10 +7339,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>110589936</v>
+        <v>120536903</v>
       </c>
       <c r="B60" t="n">
-        <v>78578</v>
+        <v>90965</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7359,37 +7355,41 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Näsåker, Ång</t>
+          <t>Lidgatu, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>599856.2841013347</v>
+        <v>599813</v>
       </c>
       <c r="R60" t="n">
-        <v>7034759.22969401</v>
+        <v>7034818</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7413,22 +7413,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2023-06-03</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2023-06-03</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7443,22 +7443,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Felicia Skorsdal</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Felicia Skorsdal</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120536903</v>
+        <v>120536900</v>
       </c>
       <c r="B61" t="n">
-        <v>90965</v>
+        <v>90679</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7471,21 +7471,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>599813</v>
+        <v>599871</v>
       </c>
       <c r="R61" t="n">
         <v>7034818</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7571,7 +7571,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120536900</v>
+        <v>120536904</v>
       </c>
       <c r="B62" t="n">
         <v>90679</v>
@@ -7615,13 +7615,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>599871</v>
+        <v>599766</v>
       </c>
       <c r="R62" t="n">
-        <v>7034818</v>
+        <v>7034808</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7687,10 +7687,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120536904</v>
+        <v>120536901</v>
       </c>
       <c r="B63" t="n">
-        <v>90679</v>
+        <v>90965</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7703,21 +7703,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7731,13 +7731,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>599766</v>
+        <v>599866</v>
       </c>
       <c r="R63" t="n">
-        <v>7034808</v>
+        <v>7034826</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7803,10 +7803,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120536901</v>
+        <v>120536902</v>
       </c>
       <c r="B64" t="n">
-        <v>90965</v>
+        <v>90679</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7819,21 +7819,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7847,13 +7847,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>599866</v>
+        <v>599814</v>
       </c>
       <c r="R64" t="n">
-        <v>7034826</v>
+        <v>7034812</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7919,10 +7919,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120536902</v>
+        <v>120536906</v>
       </c>
       <c r="B65" t="n">
-        <v>90679</v>
+        <v>88012</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7935,21 +7935,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7963,10 +7963,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>599814</v>
+        <v>599641</v>
       </c>
       <c r="R65" t="n">
-        <v>7034812</v>
+        <v>7034506</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7993,22 +7993,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8035,10 +8035,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120536906</v>
+        <v>120536905</v>
       </c>
       <c r="B66" t="n">
-        <v>88012</v>
+        <v>90965</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8051,21 +8051,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -8079,13 +8079,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>599641</v>
+        <v>599672</v>
       </c>
       <c r="R66" t="n">
-        <v>7034506</v>
+        <v>7034647</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8151,10 +8151,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120536905</v>
+        <v>120536907</v>
       </c>
       <c r="B67" t="n">
-        <v>90965</v>
+        <v>91119</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8163,25 +8163,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -8195,10 +8195,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>599672</v>
+        <v>599620</v>
       </c>
       <c r="R67" t="n">
-        <v>7034647</v>
+        <v>7034514</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8230,7 +8230,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8264,122 +8264,6 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>120536907</v>
-      </c>
-      <c r="B68" t="n">
-        <v>91119</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Lidgatu, Ång</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>599620</v>
-      </c>
-      <c r="R68" t="n">
-        <v>7034514</v>
-      </c>
-      <c r="S68" t="n">
-        <v>10</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Resele</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Maria Edstam</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Maria Edstam</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11492-2022 artfynd.xlsx
+++ b/artfynd/A 11492-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY108"/>
+  <dimension ref="A1:AZ108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157764</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157762</t>
         </is>
       </c>
     </row>
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109632333</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120536906</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102730509</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102730733</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,6 +1418,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157768</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1484,6 +1524,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157770</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1592,6 +1637,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109746428</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1700,6 +1750,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109747070</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1808,6 +1863,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109747404</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1916,6 +1976,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109747467</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2024,6 +2089,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109747554</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2121,6 +2191,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110589932</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2232,6 +2307,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120536901</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2343,6 +2423,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120536903</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2454,6 +2539,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120536905</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2551,6 +2641,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134178520</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2649,6 +2744,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102725683</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2747,6 +2847,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102730738</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2848,6 +2953,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157758</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2947,6 +3057,11 @@
       <c r="AY23" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157767</t>
         </is>
       </c>
     </row>
@@ -3050,6 +3165,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109632765</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3151,6 +3271,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109632859</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3252,6 +3377,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109632962</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3360,6 +3490,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109746431</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3468,6 +3603,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109747079</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3576,6 +3716,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109748320</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3687,6 +3832,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120536900</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3798,6 +3948,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120536902</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3909,6 +4064,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120536904</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4006,6 +4166,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134178525</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4114,6 +4279,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109747218</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4215,6 +4385,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109632969</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4312,6 +4487,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110589930</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4423,6 +4603,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120536907</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4531,6 +4716,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109748316</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4629,6 +4819,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102732283</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4730,6 +4925,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109632890</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4838,6 +5038,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109750053</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4939,6 +5144,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109632897</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5040,6 +5250,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109633116</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5148,6 +5363,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109746436</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5246,6 +5466,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102730644</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5352,6 +5577,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157756</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5453,6 +5683,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157757</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5559,6 +5794,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157760</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5658,6 +5898,11 @@
       <c r="AY49" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157769</t>
         </is>
       </c>
     </row>
@@ -5761,6 +6006,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109632757</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5869,6 +6119,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109746490</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5977,6 +6232,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109747093</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6085,6 +6345,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109749960</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6182,6 +6447,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134178107</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6290,6 +6560,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109747674</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6398,6 +6673,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109747950</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6506,6 +6786,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109748313</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6603,6 +6888,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134178642</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6701,6 +6991,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102730759</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6800,6 +7095,11 @@
       <c r="AY60" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157766</t>
         </is>
       </c>
     </row>
@@ -6903,6 +7203,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106564482</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7004,6 +7309,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109633024</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7117,6 +7427,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109746440</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7225,6 +7540,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109747391</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7322,6 +7642,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110589936</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7423,6 +7748,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109633089</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7520,6 +7850,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110589933</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7621,6 +7956,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109632938</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7726,6 +8066,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109632928</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7839,6 +8184,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109746536</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7952,6 +8302,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109747618</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8057,6 +8412,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102725610</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8163,6 +8523,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157759</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8268,6 +8633,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109633115</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8381,6 +8751,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109744815</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8494,6 +8869,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109747042</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8607,6 +8987,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109748169</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8720,6 +9105,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109749879</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8825,6 +9215,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109632324</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8930,6 +9325,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109633071</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9035,6 +9435,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109633081</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9148,6 +9553,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109745327</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9283,6 +9693,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119762301</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9418,6 +9833,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119762291</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9523,6 +9943,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109633053</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9622,6 +10047,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102731566</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9730,6 +10160,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109747166</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9829,6 +10264,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102731091</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9928,6 +10368,11 @@
       <c r="AY89" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157765</t>
         </is>
       </c>
     </row>
@@ -10032,6 +10477,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109632850</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10144,6 +10594,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109747184</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10252,6 +10707,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109747196</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10360,6 +10820,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109747422</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10472,6 +10937,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109747673</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10584,6 +11054,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109747883</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10692,6 +11167,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109747956</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10804,6 +11284,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109748041</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10902,6 +11387,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109748100</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11014,6 +11504,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109748114</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11126,6 +11621,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109749485</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11238,6 +11738,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109751231</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11350,6 +11855,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109751333</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11462,6 +11972,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109751380</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11574,6 +12089,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109751423</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11671,6 +12191,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110589937</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11768,6 +12293,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110589938</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11867,6 +12397,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102732314</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11968,8 +12503,122 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157763</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>